--- a/docs/research/triangle-msp-market/Triangle-MSP-Market-Research.xlsx
+++ b/docs/research/triangle-msp-market/Triangle-MSP-Market-Research.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Method" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Target List'!$A$1:$T$58</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Target List'!$A$1:$V$58</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="543">
   <si>
     <t xml:space="preserve">Tier</t>
   </si>
@@ -61,6 +61,12 @@
     <t xml:space="preserve">Est. rev high ($M)</t>
   </si>
   <si>
+    <t xml:space="preserve">Est. sale price low ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. sale price high ($M)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3rd-party rev est.</t>
   </si>
   <si>
@@ -1579,6 +1585,18 @@
     <t xml:space="preserve">Basis: standard MSP benchmark of ~$150-200K annual revenue per employee. Source: industry rule of thumb (Service Leadership / channel benchmarks); user-adjustable.</t>
   </si>
   <si>
+    <t xml:space="preserve">Assumed EBITDA margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA multiple - low (x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA multiple - high (x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale-price basis: est. revenue x EBITDA margin x multiple. Small SMB-focused MSPs typically trade at ~4-7x adjusted EBITDA (equivalently ~0.6-1.1x revenue at a 15% margin); high recurring-revenue mix, low client concentration, and documented processes push toward the top of the range, owner-dependence toward the bottom. Micro shops (&lt;$1M revenue) trade lower - often 0.5-1x SDE - see the small-shops tab when present.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOW TO READ THIS WORKBOOK</t>
   </si>
   <si>
@@ -1589,6 +1607,9 @@
   </si>
   <si>
     <t xml:space="preserve">'Est. rev low/high ($M)' are FORMULAS: employee band x revenue-per-employee assumptions above. Where a third-party estimate exists (ZoomInfo, Kona Equity) it is shown in its own column - those are algorithmic estimates, not filings, and are sometimes demonstrably wrong (flagged in Notes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Est. sale price low/high ($M)' are FORMULAS: est. revenue x assumed EBITDA margin x EBITDA multiple (assumptions above). These are screening-level figures only - a real valuation requires actual financials, recurring-revenue mix, and client concentration. The low uses rev-low x 4x, the high rev-high x 7x, so the range is deliberately wide.</t>
   </si>
   <si>
     <t xml:space="preserve">Employee counts come from LinkedIn-derived aggregators (ZoomInfo, LeadIQ, Crustdata, Tracxn), directory bands (Jumpfactor, DesignRush, InfoMSP), company sites, and press. They lag reality; verify via LinkedIn and direct contact before valuation work.</t>
@@ -1640,11 +1661,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1802,7 +1824,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1924,6 +1946,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2248,7 +2278,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2260,15 +2290,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2332,20 +2363,26 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.computerbilities.com","www.computerbilities.com")</f>
         <v>www.computerbilities.com</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>1995</v>
@@ -2361,7 +2398,7 @@
         <v>16</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" s="6" t="n">
         <f aca="false">IF(G2="","",ROUND(G2*Method!$B$3/1000000,1))</f>
@@ -2371,43 +2408,51 @@
         <f aca="false">IF(H2="","",ROUND(H2*Method!$B$4/1000000,1))</f>
         <v>3.2</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="L2" s="6" t="n">
+        <f aca="false">IF(J2="","",ROUND(J2*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.1</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <f aca="false">IF(K2="","",ROUND(K2*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.4</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="5"/>
+      <c r="T2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.itsco.com","www.itsco.com")</f>
         <v>www.itsco.com</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>1996</v>
@@ -2423,7 +2468,7 @@
         <v>60</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" s="6" t="n">
         <f aca="false">IF(G3="","",ROUND(G3*Method!$B$3/1000000,1))</f>
@@ -2433,45 +2478,53 @@
         <f aca="false">IF(H3="","",ROUND(H3*Method!$B$4/1000000,1))</f>
         <v>12</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="L3" s="6" t="n">
+        <f aca="false">IF(J3="","",ROUND(J3*Method!$B$6*Method!$B$7,1))</f>
+        <v>2.6</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <f aca="false">IF(K3="","",ROUND(K3*Method!$B$6*Method!$B$8,1))</f>
+        <v>12.6</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="5" t="s">
         <v>37</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="2"/>
+      <c r="S3" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="T3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U3" s="2"/>
+      <c r="V3" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.cspinc.com","www.cspinc.com")</f>
         <v>www.cspinc.com</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>1995</v>
@@ -2487,7 +2540,7 @@
         <v>45</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="6" t="n">
         <f aca="false">IF(G4="","",ROUND(G4*Method!$B$3/1000000,1))</f>
@@ -2497,39 +2550,47 @@
         <f aca="false">IF(H4="","",ROUND(H4*Method!$B$4/1000000,1))</f>
         <v>9</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>26</v>
+      <c r="L4" s="6" t="n">
+        <f aca="false">IF(J4="","",ROUND(J4*Method!$B$6*Method!$B$7,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <f aca="false">IF(K4="","",ROUND(K4*Method!$B$6*Method!$B$8,1))</f>
+        <v>9.5</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="R4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="2"/>
+      <c r="V4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.tenplus.com","www.tenplus.com")</f>
         <v>www.tenplus.com</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>1989</v>
@@ -2545,7 +2606,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J5" s="6" t="n">
         <f aca="false">IF(G5="","",ROUND(G5*Method!$B$3/1000000,1))</f>
@@ -2555,43 +2616,51 @@
         <f aca="false">IF(H5="","",ROUND(H5*Method!$B$4/1000000,1))</f>
         <v>12</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="2" t="s">
+      <c r="L5" s="6" t="n">
+        <f aca="false">IF(J5="","",ROUND(J5*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.8</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <f aca="false">IF(K5="","",ROUND(K5*Method!$B$6*Method!$B$8,1))</f>
+        <v>12.6</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="S5" s="5"/>
       <c r="T5" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="U5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="str">
         <f aca="false">HYPERLINK("https://cii.cloud","cii.cloud")</f>
         <v>cii.cloud</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1981</v>
@@ -2607,7 +2676,7 @@
         <v>49</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J6" s="6" t="n">
         <f aca="false">IF(G6="","",ROUND(G6*Method!$B$3/1000000,1))</f>
@@ -2617,41 +2686,49 @@
         <f aca="false">IF(H6="","",ROUND(H6*Method!$B$4/1000000,1))</f>
         <v>9.8</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="L6" s="6" t="n">
+        <f aca="false">IF(J6="","",ROUND(J6*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <f aca="false">IF(K6="","",ROUND(K6*Method!$B$6*Method!$B$8,1))</f>
+        <v>10.3</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="S6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3" t="str">
         <f aca="false">HYPERLINK("https://atcombts.com","atcombts.com")</f>
         <v>atcombts.com</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>1979</v>
@@ -2667,7 +2744,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">IF(G7="","",ROUND(G7*Method!$B$3/1000000,1))</f>
@@ -2677,41 +2754,49 @@
         <f aca="false">IF(H7="","",ROUND(H7*Method!$B$4/1000000,1))</f>
         <v>20</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="L7" s="6" t="n">
+        <f aca="false">IF(J7="","",ROUND(J7*Method!$B$6*Method!$B$7,1))</f>
+        <v>7.2</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <f aca="false">IF(K7="","",ROUND(K7*Method!$B$6*Method!$B$8,1))</f>
+        <v>21</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="5" t="s">
         <v>67</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="R7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="S7" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="S7" s="5"/>
       <c r="T7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="str">
         <f aca="false">HYPERLINK("https://benchmarkns.com","benchmarkns.com")</f>
         <v>benchmarkns.com</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>1992</v>
@@ -2727,7 +2812,7 @@
         <v>20</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">IF(G8="","",ROUND(G8*Method!$B$3/1000000,1))</f>
@@ -2737,39 +2822,47 @@
         <f aca="false">IF(H8="","",ROUND(H8*Method!$B$4/1000000,1))</f>
         <v>4</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>67</v>
+      <c r="L8" s="6" t="n">
+        <f aca="false">IF(J8="","",ROUND(J8*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <f aca="false">IF(K8="","",ROUND(K8*Method!$B$6*Method!$B$8,1))</f>
+        <v>4.2</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q8" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="R8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="U8" s="2"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="str">
         <f aca="false">HYPERLINK("https://rcor.com","rcor.com")</f>
         <v>rcor.com</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1992</v>
@@ -2785,7 +2878,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">IF(G9="","",ROUND(G9*Method!$B$3/1000000,1))</f>
@@ -2795,41 +2888,49 @@
         <f aca="false">IF(H9="","",ROUND(H9*Method!$B$4/1000000,1))</f>
         <v>2</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>26</v>
+      <c r="L9" s="6" t="n">
+        <f aca="false">IF(J9="","",ROUND(J9*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.4</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <f aca="false">IF(K9="","",ROUND(K9*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.1</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q9" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="R9" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="S9" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="S9" s="5"/>
       <c r="T9" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="U9" s="2"/>
+      <c r="V9" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="str">
         <f aca="false">HYPERLINK("https://thinktechadvisors.com","thinktechadvisors.com")</f>
         <v>thinktechadvisors.com</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>1999</v>
@@ -2845,7 +2946,7 @@
         <v>25</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J10" s="6" t="n">
         <f aca="false">IF(G10="","",ROUND(G10*Method!$B$3/1000000,1))</f>
@@ -2855,43 +2956,51 @@
         <f aca="false">IF(H10="","",ROUND(H10*Method!$B$4/1000000,1))</f>
         <v>5</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>67</v>
+      <c r="L10" s="6" t="n">
+        <f aca="false">IF(J10="","",ROUND(J10*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <f aca="false">IF(K10="","",ROUND(K10*Method!$B$6*Method!$B$8,1))</f>
+        <v>5.3</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="5" t="s">
         <v>89</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="S10" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="str">
         <f aca="false">HYPERLINK("https://avarianetworks.com","avarianetworks.com")</f>
         <v>avarianetworks.com</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1993</v>
@@ -2907,7 +3016,7 @@
         <v>11</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">IF(G11="","",ROUND(G11*Method!$B$3/1000000,1))</f>
@@ -2917,41 +3026,49 @@
         <f aca="false">IF(H11="","",ROUND(H11*Method!$B$4/1000000,1))</f>
         <v>2.2</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>26</v>
+      <c r="L11" s="6" t="n">
+        <f aca="false">IF(J11="","",ROUND(J11*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.7</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <f aca="false">IF(K11="","",ROUND(K11*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.3</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q11" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="R11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="S11" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="S11" s="5"/>
       <c r="T11" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="U11" s="2"/>
+      <c r="V11" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="str">
         <f aca="false">HYPERLINK("https://securena.com","securena.com")</f>
         <v>securena.com</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>2005</v>
@@ -2967,7 +3084,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">IF(G12="","",ROUND(G12*Method!$B$3/1000000,1))</f>
@@ -2977,41 +3094,49 @@
         <f aca="false">IF(H12="","",ROUND(H12*Method!$B$4/1000000,1))</f>
         <v>4</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>67</v>
+      <c r="L12" s="6" t="n">
+        <f aca="false">IF(J12="","",ROUND(J12*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.1</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <f aca="false">IF(K12="","",ROUND(K12*Method!$B$6*Method!$B$8,1))</f>
+        <v>4.2</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="5" t="s">
         <v>103</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="R12" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="5"/>
+      <c r="S12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="U12" s="2"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="str">
         <f aca="false">HYPERLINK("https://aggietechnc.com","aggietechnc.com")</f>
         <v>aggietechnc.com</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2004</v>
@@ -3027,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">IF(G13="","",ROUND(G13*Method!$B$3/1000000,1))</f>
@@ -3037,41 +3162,49 @@
         <f aca="false">IF(H13="","",ROUND(H13*Method!$B$4/1000000,1))</f>
         <v>2</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>26</v>
+      <c r="L13" s="6" t="n">
+        <f aca="false">IF(J13="","",ROUND(J13*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.3</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <f aca="false">IF(K13="","",ROUND(K13*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.1</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q13" s="5"/>
+        <v>109</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="R13" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="S13" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="S13" s="5"/>
       <c r="T13" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="U13" s="2"/>
+      <c r="V13" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.managedits.com","www.managedits.com")</f>
         <v>www.managedits.com</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>2001</v>
@@ -3087,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J14" s="6" t="n">
         <f aca="false">IF(G14="","",ROUND(G14*Method!$B$3/1000000,1))</f>
@@ -3097,41 +3230,49 @@
         <f aca="false">IF(H14="","",ROUND(H14*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>67</v>
+      <c r="L14" s="6" t="n">
+        <f aca="false">IF(J14="","",ROUND(J14*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <f aca="false">IF(K14="","",ROUND(K14*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q14" s="5"/>
+        <v>115</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="R14" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="S14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="V14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.ncmobilecomputerservices.com","www.ncmobilecomputerservices.com")</f>
         <v>www.ncmobilecomputerservices.com</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>2004</v>
@@ -3147,7 +3288,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" s="6" t="n">
         <f aca="false">IF(G15="","",ROUND(G15*Method!$B$3/1000000,1))</f>
@@ -3157,43 +3298,51 @@
         <f aca="false">IF(H15="","",ROUND(H15*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>67</v>
+      <c r="L15" s="6" t="n">
+        <f aca="false">IF(J15="","",ROUND(J15*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <f aca="false">IF(K15="","",ROUND(K15*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="R15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="S15" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="S15" s="5"/>
       <c r="T15" s="5" t="s">
         <v>124</v>
       </c>
+      <c r="U15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C16" s="3" t="str">
         <f aca="false">HYPERLINK("https://accentimaging.com","accentimaging.com")</f>
         <v>accentimaging.com</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>1984</v>
@@ -3209,7 +3358,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J16" s="6" t="n">
         <f aca="false">IF(G16="","",ROUND(G16*Method!$B$3/1000000,1))</f>
@@ -3219,43 +3368,51 @@
         <f aca="false">IF(H16="","",ROUND(H16*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>51</v>
+      <c r="L16" s="6" t="n">
+        <f aca="false">IF(J16="","",ROUND(J16*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <f aca="false">IF(K16="","",ROUND(K16*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q16" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="S16" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="S16" s="5"/>
       <c r="T16" s="5" t="s">
         <v>131</v>
       </c>
+      <c r="U16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C17" s="3" t="str">
         <f aca="false">HYPERLINK("https://amfrontier.net","amfrontier.net")</f>
         <v>amfrontier.net</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>1996</v>
@@ -3271,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="6" t="n">
         <f aca="false">IF(G17="","",ROUND(G17*Method!$B$3/1000000,1))</f>
@@ -3281,39 +3438,47 @@
         <f aca="false">IF(H17="","",ROUND(H17*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>51</v>
+      <c r="L17" s="6" t="n">
+        <f aca="false">IF(J17="","",ROUND(J17*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <f aca="false">IF(K17="","",ROUND(K17*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q17" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R17" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="S17" s="2"/>
-      <c r="T17" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="U17" s="2"/>
+      <c r="V17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C18" s="3" t="str">
         <f aca="false">HYPERLINK("https://sysnettech.com","sysnettech.com")</f>
         <v>sysnettech.com</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -3324,7 +3489,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J18" s="6" t="n">
         <f aca="false">IF(G18="","",ROUND(G18*Method!$B$3/1000000,1))</f>
@@ -3334,39 +3499,47 @@
         <f aca="false">IF(H18="","",ROUND(H18*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>51</v>
+      <c r="L18" s="6" t="n">
+        <f aca="false">IF(J18="","",ROUND(J18*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <f aca="false">IF(K18="","",ROUND(K18*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q18" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R18" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="S18" s="2"/>
-      <c r="T18" s="5"/>
+        <v>140</v>
+      </c>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="U18" s="2"/>
+      <c r="V18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C19" s="3" t="str">
         <f aca="false">HYPERLINK("https://lightwireinc.com","lightwireinc.com")</f>
         <v>lightwireinc.com</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -3377,7 +3550,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J19" s="6" t="n">
         <f aca="false">IF(G19="","",ROUND(G19*Method!$B$3/1000000,1))</f>
@@ -3387,41 +3560,49 @@
         <f aca="false">IF(H19="","",ROUND(H19*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>51</v>
+      <c r="L19" s="6" t="n">
+        <f aca="false">IF(J19="","",ROUND(J19*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <f aca="false">IF(K19="","",ROUND(K19*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q19" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="R19" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="S19" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="V19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C20" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.wingswept.com","www.wingswept.com")</f>
         <v>www.wingswept.com</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>1995</v>
@@ -3437,7 +3618,7 @@
         <v>85</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J20" s="11" t="n">
         <f aca="false">IF(G20="","",ROUND(G20*Method!$B$3/1000000,1))</f>
@@ -3447,43 +3628,51 @@
         <f aca="false">IF(H20="","",ROUND(H20*Method!$B$4/1000000,1))</f>
         <v>17</v>
       </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="O20" s="7" t="s">
+      <c r="L20" s="11" t="n">
+        <f aca="false">IF(J20="","",ROUND(J20*Method!$B$6*Method!$B$7,1))</f>
+        <v>6.1</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <f aca="false">IF(K20="","",ROUND(K20*Method!$B$6*Method!$B$8,1))</f>
+        <v>17.9</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="Q20" s="10"/>
+      <c r="Q20" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R20" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="S20" s="7" t="s">
         <v>153</v>
       </c>
+      <c r="S20" s="10"/>
       <c r="T20" s="10" t="s">
         <v>154</v>
       </c>
+      <c r="U20" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="V20" s="10" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C21" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.netfriends.com","www.netfriends.com")</f>
         <v>www.netfriends.com</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>1997</v>
@@ -3499,7 +3688,7 @@
         <v>60</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">IF(G21="","",ROUND(G21*Method!$B$3/1000000,1))</f>
@@ -3509,45 +3698,53 @@
         <f aca="false">IF(H21="","",ROUND(H21*Method!$B$4/1000000,1))</f>
         <v>12</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="N21" s="10" t="s">
+      <c r="L21" s="11" t="n">
+        <f aca="false">IF(J21="","",ROUND(J21*Method!$B$6*Method!$B$7,1))</f>
+        <v>4.5</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <f aca="false">IF(K21="","",ROUND(K21*Method!$B$6*Method!$B$8,1))</f>
+        <v>12.6</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>150</v>
+      <c r="O21" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q21" s="10"/>
+        <v>161</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R21" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="S21" s="7" t="s">
         <v>162</v>
       </c>
+      <c r="S21" s="10"/>
       <c r="T21" s="10" t="s">
         <v>163</v>
       </c>
+      <c r="U21" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="V21" s="10" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.worksmart.com","www.worksmart.com")</f>
         <v>www.worksmart.com</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>2001</v>
@@ -3563,7 +3760,7 @@
         <v>100</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">IF(G22="","",ROUND(G22*Method!$B$3/1000000,1))</f>
@@ -3573,45 +3770,53 @@
         <f aca="false">IF(H22="","",ROUND(H22*Method!$B$4/1000000,1))</f>
         <v>20</v>
       </c>
-      <c r="L22" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="N22" s="10" t="s">
+      <c r="L22" s="11" t="n">
+        <f aca="false">IF(J22="","",ROUND(J22*Method!$B$6*Method!$B$7,1))</f>
+        <v>7.2</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <f aca="false">IF(K22="","",ROUND(K22*Method!$B$6*Method!$B$8,1))</f>
+        <v>21</v>
+      </c>
+      <c r="N22" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="O22" s="7" t="s">
-        <v>67</v>
+      <c r="O22" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q22" s="10"/>
+        <v>171</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="R22" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="S22" s="7" t="s">
         <v>172</v>
       </c>
+      <c r="S22" s="10"/>
       <c r="T22" s="10" t="s">
         <v>173</v>
       </c>
+      <c r="U22" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="V22" s="10" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C23" s="8" t="str">
         <f aca="false">HYPERLINK("https://samitsolutions.com","samitsolutions.com")</f>
         <v>samitsolutions.com</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>2009</v>
@@ -3627,7 +3832,7 @@
         <v>38</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J23" s="11" t="n">
         <f aca="false">IF(G23="","",ROUND(G23*Method!$B$3/1000000,1))</f>
@@ -3637,43 +3842,51 @@
         <f aca="false">IF(H23="","",ROUND(H23*Method!$B$4/1000000,1))</f>
         <v>7.6</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>150</v>
+      <c r="L23" s="11" t="n">
+        <f aca="false">IF(J23="","",ROUND(J23*Method!$B$6*Method!$B$7,1))</f>
+        <v>2.7</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <f aca="false">IF(K23="","",ROUND(K23*Method!$B$6*Method!$B$8,1))</f>
+        <v>8</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q23" s="10"/>
+        <v>180</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R23" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="S23" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="T23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="V23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C24" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.xceedit.com","www.xceedit.com")</f>
         <v>www.xceedit.com</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>2009</v>
@@ -3689,7 +3902,7 @@
         <v>15</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J24" s="11" t="n">
         <f aca="false">IF(G24="","",ROUND(G24*Method!$B$3/1000000,1))</f>
@@ -3699,43 +3912,51 @@
         <f aca="false">IF(H24="","",ROUND(H24*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>150</v>
+      <c r="L24" s="11" t="n">
+        <f aca="false">IF(J24="","",ROUND(J24*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.7</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <f aca="false">IF(K24="","",ROUND(K24*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q24" s="10"/>
+        <v>188</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R24" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="S24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="T24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="V24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C25" s="8" t="str">
         <f aca="false">HYPERLINK("https://enitechsolutions.com","enitechsolutions.com")</f>
         <v>enitechsolutions.com</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>2013</v>
@@ -3751,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J25" s="11" t="n">
         <f aca="false">IF(G25="","",ROUND(G25*Method!$B$3/1000000,1))</f>
@@ -3761,43 +3982,51 @@
         <f aca="false">IF(H25="","",ROUND(H25*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>150</v>
+      <c r="L25" s="11" t="n">
+        <f aca="false">IF(J25="","",ROUND(J25*Method!$B$6*Method!$B$7,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <f aca="false">IF(K25="","",ROUND(K25*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N25" s="7"/>
+      <c r="O25" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q25" s="10"/>
+        <v>194</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R25" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="S25" s="7" t="s">
         <v>195</v>
       </c>
+      <c r="S25" s="10"/>
       <c r="T25" s="10" t="s">
         <v>196</v>
       </c>
+      <c r="U25" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="V25" s="10" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C26" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.onpartech.com","www.onpartech.com")</f>
         <v>www.onpartech.com</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>2007</v>
@@ -3813,7 +4042,7 @@
         <v>12</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J26" s="11" t="n">
         <f aca="false">IF(G26="","",ROUND(G26*Method!$B$3/1000000,1))</f>
@@ -3823,43 +4052,51 @@
         <f aca="false">IF(H26="","",ROUND(H26*Method!$B$4/1000000,1))</f>
         <v>2.4</v>
       </c>
-      <c r="L26" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>67</v>
+      <c r="L26" s="11" t="n">
+        <f aca="false">IF(J26="","",ROUND(J26*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.7</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <f aca="false">IF(K26="","",ROUND(K26*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.5</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q26" s="10"/>
+        <v>202</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="R26" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="S26" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="T26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="V26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C27" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.insighttechadv.com","www.insighttechadv.com")</f>
         <v>www.insighttechadv.com</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>2019</v>
@@ -3875,7 +4112,7 @@
         <v>15</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J27" s="11" t="n">
         <f aca="false">IF(G27="","",ROUND(G27*Method!$B$3/1000000,1))</f>
@@ -3885,43 +4122,51 @@
         <f aca="false">IF(H27="","",ROUND(H27*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>67</v>
+      <c r="L27" s="11" t="n">
+        <f aca="false">IF(J27="","",ROUND(J27*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <f aca="false">IF(K27="","",ROUND(K27*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N27" s="7"/>
+      <c r="O27" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q27" s="10"/>
+        <v>210</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="R27" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="S27" s="7" t="s">
         <v>211</v>
       </c>
+      <c r="S27" s="10"/>
       <c r="T27" s="10" t="s">
         <v>212</v>
       </c>
+      <c r="U27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="V27" s="10" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C28" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.wellforceit.com","www.wellforceit.com")</f>
         <v>www.wellforceit.com</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>2019</v>
@@ -3937,7 +4182,7 @@
         <v>18</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J28" s="11" t="n">
         <f aca="false">IF(G28="","",ROUND(G28*Method!$B$3/1000000,1))</f>
@@ -3947,41 +4192,49 @@
         <f aca="false">IF(H28="","",ROUND(H28*Method!$B$4/1000000,1))</f>
         <v>3.6</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>150</v>
+      <c r="L28" s="11" t="n">
+        <f aca="false">IF(J28="","",ROUND(J28*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.1</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <f aca="false">IF(K28="","",ROUND(K28*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.8</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q28" s="10" t="s">
         <v>219</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="R28" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="10"/>
+      <c r="S28" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="T28" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="U28" s="7"/>
+      <c r="V28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C29" s="8" t="str">
         <f aca="false">HYPERLINK("https://petronellatech.com","petronellatech.com")</f>
         <v>petronellatech.com</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>2002</v>
@@ -3997,7 +4250,7 @@
         <v>10</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J29" s="11" t="n">
         <f aca="false">IF(G29="","",ROUND(G29*Method!$B$3/1000000,1))</f>
@@ -4007,45 +4260,53 @@
         <f aca="false">IF(H29="","",ROUND(H29*Method!$B$4/1000000,1))</f>
         <v>2</v>
       </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>67</v>
+      <c r="L29" s="11" t="n">
+        <f aca="false">IF(J29="","",ROUND(J29*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.4</v>
+      </c>
+      <c r="M29" s="11" t="n">
+        <f aca="false">IF(K29="","",ROUND(K29*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.1</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q29" s="10" t="s">
         <v>225</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="R29" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>116</v>
+      <c r="S29" s="10" t="s">
+        <v>227</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="V29" s="10" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C30" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.freedomtech.us","www.freedomtech.us")</f>
         <v>www.freedomtech.us</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>2011</v>
@@ -4061,7 +4322,7 @@
         <v>30</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J30" s="11" t="n">
         <f aca="false">IF(G30="","",ROUND(G30*Method!$B$3/1000000,1))</f>
@@ -4071,39 +4332,47 @@
         <f aca="false">IF(H30="","",ROUND(H30*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="S30" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="T30" s="10"/>
+      <c r="L30" s="11" t="n">
+        <f aca="false">IF(J30="","",ROUND(J30*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M30" s="11" t="n">
+        <f aca="false">IF(K30="","",ROUND(K30*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="P30" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="V30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C31" s="8" t="str">
         <f aca="false">HYPERLINK("https://connectcause.com","connectcause.com")</f>
         <v>connectcause.com</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -4114,7 +4383,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J31" s="11" t="n">
         <f aca="false">IF(G31="","",ROUND(G31*Method!$B$3/1000000,1))</f>
@@ -4124,39 +4393,47 @@
         <f aca="false">IF(H31="","",ROUND(H31*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="T31" s="10"/>
+      <c r="L31" s="11" t="n">
+        <f aca="false">IF(J31="","",ROUND(J31*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M31" s="11" t="n">
+        <f aca="false">IF(K31="","",ROUND(K31*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="U31" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="V31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C32" s="8" t="str">
         <f aca="false">HYPERLINK("https://bentontechsolutions.com","bentontechsolutions.com")</f>
         <v>bentontechsolutions.com</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -4167,7 +4444,7 @@
         <v>15</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J32" s="11" t="n">
         <f aca="false">IF(G32="","",ROUND(G32*Method!$B$3/1000000,1))</f>
@@ -4177,39 +4454,47 @@
         <f aca="false">IF(H32="","",ROUND(H32*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="S32" s="7" t="s">
+      <c r="L32" s="11" t="n">
+        <f aca="false">IF(J32="","",ROUND(J32*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <f aca="false">IF(K32="","",ROUND(K32*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="T32" s="10"/>
+      <c r="P32" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="U32" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="V32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C33" s="8" t="str">
         <f aca="false">HYPERLINK("https://intelligentvisibility.com","intelligentvisibility.com")</f>
         <v>intelligentvisibility.com</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -4220,7 +4505,7 @@
         <v>60</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J33" s="11" t="n">
         <f aca="false">IF(G33="","",ROUND(G33*Method!$B$3/1000000,1))</f>
@@ -4230,39 +4515,47 @@
         <f aca="false">IF(H33="","",ROUND(H33*Method!$B$4/1000000,1))</f>
         <v>12</v>
       </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="S33" s="7"/>
+      <c r="L33" s="11" t="n">
+        <f aca="false">IF(J33="","",ROUND(J33*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.8</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <f aca="false">IF(K33="","",ROUND(K33*Method!$B$6*Method!$B$8,1))</f>
+        <v>12.6</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
       <c r="T33" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
+      </c>
+      <c r="U33" s="7"/>
+      <c r="V33" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C34" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.itguys.net","www.itguys.net")</f>
         <v>www.itguys.net</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>2017</v>
@@ -4278,7 +4571,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J34" s="11" t="n">
         <f aca="false">IF(G34="","",ROUND(G34*Method!$B$3/1000000,1))</f>
@@ -4288,41 +4581,49 @@
         <f aca="false">IF(H34="","",ROUND(H34*Method!$B$4/1000000,1))</f>
         <v>2</v>
       </c>
-      <c r="L34" s="7"/>
-      <c r="M34" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>150</v>
+      <c r="L34" s="11" t="n">
+        <f aca="false">IF(J34="","",ROUND(J34*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <f aca="false">IF(K34="","",ROUND(K34*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.1</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q34" s="10"/>
+        <v>250</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="R34" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="S34" s="7"/>
+        <v>251</v>
+      </c>
+      <c r="S34" s="10"/>
       <c r="T34" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="U34" s="7"/>
+      <c r="V34" s="10" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C35" s="13" t="str">
         <f aca="false">HYPERLINK("https://technologyassociates.net","technologyassociates.net")</f>
         <v>technologyassociates.net</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>1997</v>
@@ -4338,7 +4639,7 @@
         <v>40</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J35" s="16" t="n">
         <f aca="false">IF(G35="","",ROUND(G35*Method!$B$3/1000000,1))</f>
@@ -4348,43 +4649,51 @@
         <f aca="false">IF(H35="","",ROUND(H35*Method!$B$4/1000000,1))</f>
         <v>8</v>
       </c>
-      <c r="L35" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="N35" s="15" t="s">
+      <c r="L35" s="16" t="n">
+        <f aca="false">IF(J35="","",ROUND(J35*Method!$B$6*Method!$B$7,1))</f>
+        <v>2.7</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <f aca="false">IF(K35="","",ROUND(K35*Method!$B$6*Method!$B$8,1))</f>
+        <v>8.4</v>
+      </c>
+      <c r="N35" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="O35" s="12" t="s">
+      <c r="O35" s="15" t="s">
         <v>257</v>
       </c>
       <c r="P35" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="Q35" s="15"/>
+      <c r="Q35" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="R35" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="S35" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="T35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="V35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C36" s="13" t="str">
         <f aca="false">HYPERLINK("https://harborit.com","harborit.com")</f>
         <v>harborit.com</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E36" s="14" t="n">
         <v>1990</v>
@@ -4400,7 +4709,7 @@
         <v>49</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J36" s="16" t="n">
         <f aca="false">IF(G36="","",ROUND(G36*Method!$B$3/1000000,1))</f>
@@ -4410,45 +4719,53 @@
         <f aca="false">IF(H36="","",ROUND(H36*Method!$B$4/1000000,1))</f>
         <v>9.8</v>
       </c>
-      <c r="L36" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="N36" s="15" t="s">
+      <c r="L36" s="16" t="n">
+        <f aca="false">IF(J36="","",ROUND(J36*Method!$B$6*Method!$B$7,1))</f>
+        <v>3.6</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <f aca="false">IF(K36="","",ROUND(K36*Method!$B$6*Method!$B$8,1))</f>
+        <v>10.3</v>
+      </c>
+      <c r="N36" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="O36" s="12" t="s">
-        <v>257</v>
+      <c r="O36" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="P36" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q36" s="15"/>
+        <v>268</v>
+      </c>
+      <c r="Q36" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="R36" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="S36" s="12" t="s">
         <v>269</v>
       </c>
+      <c r="S36" s="15"/>
       <c r="T36" s="15" t="s">
         <v>270</v>
       </c>
+      <c r="U36" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="V36" s="15" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C37" s="13" t="str">
         <f aca="false">HYPERLINK("https://pc-net.com","pc-net.com")</f>
         <v>pc-net.com</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>1987</v>
@@ -4464,7 +4781,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J37" s="16" t="n">
         <f aca="false">IF(G37="","",ROUND(G37*Method!$B$3/1000000,1))</f>
@@ -4474,41 +4791,49 @@
         <f aca="false">IF(H37="","",ROUND(H37*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L37" s="12"/>
-      <c r="M37" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="N37" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>257</v>
+      <c r="L37" s="16" t="n">
+        <f aca="false">IF(J37="","",ROUND(J37*Method!$B$6*Method!$B$7,1))</f>
+        <v>1</v>
+      </c>
+      <c r="M37" s="16" t="n">
+        <f aca="false">IF(K37="","",ROUND(K37*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N37" s="12"/>
+      <c r="O37" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="P37" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q37" s="15"/>
+        <v>277</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="R37" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="T37" s="15"/>
+        <v>260</v>
+      </c>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="U37" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="V37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C38" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.scarlettgroup.com","www.scarlettgroup.com")</f>
         <v>www.scarlettgroup.com</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E38" s="14" t="n">
         <v>2005</v>
@@ -4524,7 +4849,7 @@
         <v>99</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J38" s="16" t="n">
         <f aca="false">IF(G38="","",ROUND(G38*Method!$B$3/1000000,1))</f>
@@ -4534,39 +4859,47 @@
         <f aca="false">IF(H38="","",ROUND(H38*Method!$B$4/1000000,1))</f>
         <v>19.8</v>
       </c>
-      <c r="L38" s="12"/>
-      <c r="M38" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="N38" s="15"/>
-      <c r="O38" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q38" s="15"/>
+      <c r="L38" s="16" t="n">
+        <f aca="false">IF(J38="","",ROUND(J38*Method!$B$6*Method!$B$7,1))</f>
+        <v>2.3</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <f aca="false">IF(K38="","",ROUND(K38*Method!$B$6*Method!$B$8,1))</f>
+        <v>20.8</v>
+      </c>
+      <c r="N38" s="12"/>
+      <c r="O38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="R38" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="S38" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="T38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="U38" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="V38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C39" s="18" t="str">
         <f aca="false">HYPERLINK("https://cmitsolutions.com/cary-nc-1008/","cmitsolutions.com/cary-nc-1008")</f>
         <v>cmitsolutions.com/cary-nc-1008</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
@@ -4577,7 +4910,7 @@
         <v>15</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J39" s="21" t="n">
         <f aca="false">IF(G39="","",ROUND(G39*Method!$B$3/1000000,1))</f>
@@ -4587,41 +4920,49 @@
         <f aca="false">IF(H39="","",ROUND(H39*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L39" s="17"/>
-      <c r="M39" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="N39" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="O39" s="17" t="s">
-        <v>67</v>
+      <c r="L39" s="21" t="n">
+        <f aca="false">IF(J39="","",ROUND(J39*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M39" s="21" t="n">
+        <f aca="false">IF(K39="","",ROUND(K39*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N39" s="17"/>
+      <c r="O39" s="20" t="s">
+        <v>291</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q39" s="20"/>
+        <v>292</v>
+      </c>
+      <c r="Q39" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="R39" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="S39" s="17"/>
+        <v>293</v>
+      </c>
+      <c r="S39" s="20"/>
       <c r="T39" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
+      </c>
+      <c r="U39" s="17"/>
+      <c r="V39" s="20" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C40" s="18" t="str">
         <f aca="false">HYPERLINK("https://cmitsolutions.com/chapelhill-nc-1074/","cmitsolutions.com/chapelhill-nc-1074")</f>
         <v>cmitsolutions.com/chapelhill-nc-1074</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
@@ -4632,7 +4973,7 @@
         <v>8</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J40" s="21" t="n">
         <f aca="false">IF(G40="","",ROUND(G40*Method!$B$3/1000000,1))</f>
@@ -4642,39 +4983,47 @@
         <f aca="false">IF(H40="","",ROUND(H40*Method!$B$4/1000000,1))</f>
         <v>1.6</v>
       </c>
-      <c r="L40" s="17"/>
-      <c r="M40" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="N40" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="O40" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20" t="s">
+      <c r="L40" s="21" t="n">
+        <f aca="false">IF(J40="","",ROUND(J40*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.2</v>
+      </c>
+      <c r="M40" s="21" t="n">
+        <f aca="false">IF(K40="","",ROUND(K40*Method!$B$6*Method!$B$8,1))</f>
+        <v>1.7</v>
+      </c>
+      <c r="N40" s="17"/>
+      <c r="O40" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="S40" s="17"/>
+      <c r="P40" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q40" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
       <c r="T40" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
+      </c>
+      <c r="U40" s="17"/>
+      <c r="V40" s="20" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C41" s="18" t="str">
         <f aca="false">HYPERLINK("https://www.teamlogicit.com/durhamnc311/","www.teamlogicit.com/durhamnc311")</f>
         <v>www.teamlogicit.com/durhamnc311</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E41" s="19" t="n">
         <v>2018</v>
@@ -4690,7 +5039,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J41" s="21" t="n">
         <f aca="false">IF(G41="","",ROUND(G41*Method!$B$3/1000000,1))</f>
@@ -4700,43 +5049,51 @@
         <f aca="false">IF(H41="","",ROUND(H41*Method!$B$4/1000000,1))</f>
         <v>2.4</v>
       </c>
-      <c r="L41" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="M41" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="N41" s="20" t="s">
+      <c r="L41" s="21" t="n">
+        <f aca="false">IF(J41="","",ROUND(J41*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="21" t="n">
+        <f aca="false">IF(K41="","",ROUND(K41*Method!$B$6*Method!$B$8,1))</f>
+        <v>2.5</v>
+      </c>
+      <c r="N41" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="O41" s="17" t="s">
-        <v>67</v>
+      <c r="O41" s="20" t="s">
+        <v>306</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q41" s="20"/>
+        <v>307</v>
+      </c>
+      <c r="Q41" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="R41" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="S41" s="17"/>
+        <v>308</v>
+      </c>
+      <c r="S41" s="20"/>
       <c r="T41" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
+      </c>
+      <c r="U41" s="17"/>
+      <c r="V41" s="20" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C42" s="18" t="str">
         <f aca="false">HYPERLINK("https://www.teamlogicit.com/CarrboroNC316/","www.teamlogicit.com/CarrboroNC316")</f>
         <v>www.teamlogicit.com/CarrboroNC316</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -4747,7 +5104,7 @@
         <v>8</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J42" s="21" t="n">
         <f aca="false">IF(G42="","",ROUND(G42*Method!$B$3/1000000,1))</f>
@@ -4757,39 +5114,47 @@
         <f aca="false">IF(H42="","",ROUND(H42*Method!$B$4/1000000,1))</f>
         <v>1.6</v>
       </c>
-      <c r="L42" s="17"/>
-      <c r="M42" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="N42" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="O42" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20" t="s">
+      <c r="L42" s="21" t="n">
+        <f aca="false">IF(J42="","",ROUND(J42*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.2</v>
+      </c>
+      <c r="M42" s="21" t="n">
+        <f aca="false">IF(K42="","",ROUND(K42*Method!$B$6*Method!$B$8,1))</f>
+        <v>1.7</v>
+      </c>
+      <c r="N42" s="17"/>
+      <c r="O42" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="S42" s="17"/>
+      <c r="P42" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q42" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
       <c r="T42" s="20" t="s">
-        <v>299</v>
+        <v>315</v>
+      </c>
+      <c r="U42" s="17"/>
+      <c r="V42" s="20" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C43" s="18" t="str">
         <f aca="false">HYPERLINK("https://www.teamlogicit.com/raleighnc304/","www.teamlogicit.com/raleighnc304")</f>
         <v>www.teamlogicit.com/raleighnc304</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -4800,7 +5165,7 @@
         <v>30</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J43" s="21" t="n">
         <f aca="false">IF(G43="","",ROUND(G43*Method!$B$3/1000000,1))</f>
@@ -4810,39 +5175,47 @@
         <f aca="false">IF(H43="","",ROUND(H43*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L43" s="17"/>
-      <c r="M43" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="N43" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="O43" s="17" t="s">
-        <v>257</v>
+      <c r="L43" s="21" t="n">
+        <f aca="false">IF(J43="","",ROUND(J43*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M43" s="21" t="n">
+        <f aca="false">IF(K43="","",ROUND(K43*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N43" s="17"/>
+      <c r="O43" s="20" t="s">
+        <v>319</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q43" s="20"/>
+        <v>320</v>
+      </c>
+      <c r="Q43" s="17" t="s">
+        <v>259</v>
+      </c>
       <c r="R43" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="S43" s="17"/>
-      <c r="T43" s="20"/>
+        <v>321</v>
+      </c>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="U43" s="17"/>
+      <c r="V43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C44" s="8" t="str">
         <f aca="false">HYPERLINK("https://coremanaged.com","coremanaged.com")</f>
         <v>coremanaged.com</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -4852,36 +5225,38 @@
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
-      <c r="M44" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="S44" s="7"/>
-      <c r="T44" s="10"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="U44" s="7"/>
+      <c r="V44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C45" s="8" t="str">
         <f aca="false">HYPERLINK("https://tek-help.com","tek-help.com")</f>
         <v>tek-help.com</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -4891,36 +5266,38 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
-      <c r="M45" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O45" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="10"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="U45" s="7"/>
+      <c r="V45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C46" s="8" t="str">
         <f aca="false">HYPERLINK("https://trianglecomputerservices.com","trianglecomputerservices.com")</f>
         <v>trianglecomputerservices.com</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -4930,38 +5307,40 @@
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
-      <c r="M46" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O46" s="7" t="s">
-        <v>51</v>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q46" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="R46" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="S46" s="7"/>
-      <c r="T46" s="10"/>
+        <v>330</v>
+      </c>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="U46" s="7"/>
+      <c r="V46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C47" s="8" t="str">
         <f aca="false">HYPERLINK("https://csi-of-raleigh.com","csi-of-raleigh.com")</f>
         <v>csi-of-raleigh.com</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
@@ -4971,36 +5350,38 @@
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
-      <c r="M47" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O47" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="S47" s="7"/>
-      <c r="T47" s="10"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="U47" s="7"/>
+      <c r="V47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C48" s="8" t="str">
         <f aca="false">HYPERLINK("https://exinent.com","exinent.com")</f>
         <v>exinent.com</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
@@ -5011,7 +5392,7 @@
         <v>99</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J48" s="11" t="n">
         <f aca="false">IF(G48="","",ROUND(G48*Method!$B$3/1000000,1))</f>
@@ -5021,43 +5402,51 @@
         <f aca="false">IF(H48="","",ROUND(H48*Method!$B$4/1000000,1))</f>
         <v>19.8</v>
       </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N48" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>51</v>
+      <c r="L48" s="11" t="n">
+        <f aca="false">IF(J48="","",ROUND(J48*Method!$B$6*Method!$B$7,1))</f>
+        <v>4.5</v>
+      </c>
+      <c r="M48" s="11" t="n">
+        <f aca="false">IF(K48="","",ROUND(K48*Method!$B$6*Method!$B$8,1))</f>
+        <v>20.8</v>
+      </c>
+      <c r="N48" s="7"/>
+      <c r="O48" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q48" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="Q48" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="R48" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="S48" s="7" t="s">
         <v>336</v>
       </c>
+      <c r="S48" s="10"/>
       <c r="T48" s="10" t="s">
         <v>337</v>
       </c>
+      <c r="U48" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="V48" s="10" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C49" s="8" t="str">
         <f aca="false">HYPERLINK("https://cadinc.com","cadinc.com")</f>
         <v>cadinc.com</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
@@ -5067,38 +5456,40 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
-      <c r="M49" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="S49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
       <c r="T49" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="U49" s="7"/>
+      <c r="V49" s="10" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C50" s="8" t="str">
         <f aca="false">HYPERLINK("https://us.aap3.com","us.aap3.com")</f>
         <v>us.aap3.com</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -5109,7 +5500,7 @@
         <v>80</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J50" s="11" t="n">
         <f aca="false">IF(G50="","",ROUND(G50*Method!$B$3/1000000,1))</f>
@@ -5119,39 +5510,47 @@
         <f aca="false">IF(H50="","",ROUND(H50*Method!$B$4/1000000,1))</f>
         <v>16</v>
       </c>
-      <c r="L50" s="7"/>
-      <c r="M50" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="N50" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O50" s="7" t="s">
-        <v>257</v>
+      <c r="L50" s="11" t="n">
+        <f aca="false">IF(J50="","",ROUND(J50*Method!$B$6*Method!$B$7,1))</f>
+        <v>2.7</v>
+      </c>
+      <c r="M50" s="11" t="n">
+        <f aca="false">IF(K50="","",ROUND(K50*Method!$B$6*Method!$B$8,1))</f>
+        <v>16.8</v>
+      </c>
+      <c r="N50" s="7"/>
+      <c r="O50" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q50" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>259</v>
+      </c>
       <c r="R50" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="S50" s="7"/>
-      <c r="T50" s="10"/>
+        <v>347</v>
+      </c>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="U50" s="7"/>
+      <c r="V50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C51" s="8" t="str">
         <f aca="false">HYPERLINK("https://macvantage.com","macvantage.com")</f>
         <v>macvantage.com</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
@@ -5161,37 +5560,39 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O51" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>349</v>
-      </c>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
       <c r="T51" s="10" t="s">
         <v>350</v>
       </c>
+      <c r="U51" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="V51" s="10" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E52" s="9" t="n">
         <v>2016</v>
@@ -5206,115 +5607,121 @@
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N52" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O52" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="S52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
       <c r="T52" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
+      </c>
+      <c r="U52" s="7"/>
+      <c r="V52" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O53" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="S53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
       <c r="T53" s="10" t="s">
-        <v>354</v>
+        <v>359</v>
+      </c>
+      <c r="U53" s="7"/>
+      <c r="V53" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O54" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="S54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
       <c r="T54" s="10" t="s">
-        <v>354</v>
+        <v>361</v>
+      </c>
+      <c r="U54" s="7"/>
+      <c r="V54" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
@@ -5324,35 +5731,37 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c r="M55" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="S55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
       <c r="T55" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
+      </c>
+      <c r="U55" s="7"/>
+      <c r="V55" s="10" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
@@ -5362,35 +5771,37 @@
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
-      <c r="M56" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N56" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O56" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="S56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
       <c r="T56" s="10" t="s">
-        <v>354</v>
+        <v>366</v>
+      </c>
+      <c r="U56" s="7"/>
+      <c r="V56" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -5400,35 +5811,37 @@
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O57" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="S57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
       <c r="T57" s="10" t="s">
-        <v>354</v>
+        <v>369</v>
+      </c>
+      <c r="U57" s="7"/>
+      <c r="V57" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
@@ -5438,27 +5851,29 @@
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
-      <c r="M58" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="N58" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="O58" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="S58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="7"/>
+      <c r="O58" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q58" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
       <c r="T58" s="10" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="U58" s="7"/>
+      <c r="V58" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T58"/>
+  <autoFilter ref="A1:V58"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5490,299 +5905,299 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" s="24" t="n">
         <v>1997</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C3" s="24" t="n">
         <v>1990</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>1987</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>2011</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>1998</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>2014</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>1995</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>1997</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -5814,307 +6229,307 @@
         <v>1</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -6133,7 +6548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130"/>
@@ -6142,12 +6557,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B2" s="29" t="n">
         <v>2026</v>
@@ -6155,7 +6570,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B3" s="30" t="n">
         <v>150000</v>
@@ -6163,7 +6578,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B4" s="30" t="n">
         <v>200000</v>
@@ -6171,114 +6586,148 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>516</v>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28"/>
+      <c r="A7" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B7" s="32" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
-        <v>526</v>
-      </c>
+      <c r="A18" s="28"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28"/>
+      <c r="A19" s="27" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="s">
-        <v>527</v>
+      <c r="A20" s="28" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>531</v>
-      </c>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>532</v>
+      <c r="A25" s="27" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>535</v>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>
